--- a/branches/fix/publish-simplifier-command/StructureDefinition-LogicalModelMolGen.xlsx
+++ b/branches/fix/publish-simplifier-command/StructureDefinition-LogicalModelMolGen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:37:37+00:00</t>
+    <t>2026-09-03T10:52:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
